--- a/fixed_trading_daily_volatile.xlsx
+++ b/fixed_trading_daily_volatile.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:M87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2331,6 +2331,2556 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2025-09-10T07:35:08</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_trading_daily_volatile_runs_batch</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>trial_000</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>0.251</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.7615</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.2544</v>
+      </c>
+      <c r="H38" t="n">
+        <v>-0.011</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.1338</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.1233</v>
+      </c>
+      <c r="K38" t="n">
+        <v>-0.1296</v>
+      </c>
+      <c r="L38" t="n">
+        <v>-0.0897</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 3.950916564838231e-05, "batch_size": 1024, "gamma": 0.9646752384611725, "net_dimension": 512, "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 312}, "task": "trading", "freq": "daily", "dataset": "volatile"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2025-09-10T07:39:33</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_trading_daily_volatile_runs_batch</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>trial_001</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>0.0629</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.544</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.0636</v>
+      </c>
+      <c r="H39" t="n">
+        <v>-0.1597</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.1286</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.1233</v>
+      </c>
+      <c r="K39" t="n">
+        <v>-0.1229</v>
+      </c>
+      <c r="L39" t="n">
+        <v>-0.0897</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 3.950916564838231e-05, "batch_size": 1024, "gamma": 0.9646752384611725, "net_dimension": 512, "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 313}, "task": "trading", "freq": "daily", "dataset": "volatile"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2025-09-10T07:43:56</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_trading_daily_volatile_runs_batch</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>trial_002</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>0.1781</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1.118</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.1804</v>
+      </c>
+      <c r="H40" t="n">
+        <v>-0.06859999999999999</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.1598</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.1233</v>
+      </c>
+      <c r="K40" t="n">
+        <v>-0.1559</v>
+      </c>
+      <c r="L40" t="n">
+        <v>-0.0897</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 3.950916564838231e-05, "batch_size": 1024, "gamma": 0.9646752384611725, "net_dimension": 512, "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 314}, "task": "trading", "freq": "daily", "dataset": "volatile"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2025-09-10T07:48:17</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_trading_daily_volatile_runs_batch</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>trial_003</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>0.1479</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1.299</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.1498</v>
+      </c>
+      <c r="H41" t="n">
+        <v>-0.0925</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.1124</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.1233</v>
+      </c>
+      <c r="K41" t="n">
+        <v>-0.08400000000000001</v>
+      </c>
+      <c r="L41" t="n">
+        <v>-0.0897</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 3.950916564838231e-05, "batch_size": 1024, "gamma": 0.9646752384611725, "net_dimension": 512, "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 315}, "task": "trading", "freq": "daily", "dataset": "volatile"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2025-09-10T07:52:43</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_trading_daily_volatile_runs_batch</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>trial_004</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>0.2388</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1.8123</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.242</v>
+      </c>
+      <c r="H42" t="n">
+        <v>-0.0206</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.1239</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.1233</v>
+      </c>
+      <c r="K42" t="n">
+        <v>-0.1144</v>
+      </c>
+      <c r="L42" t="n">
+        <v>-0.0897</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 3.950916564838231e-05, "batch_size": 1024, "gamma": 0.9646752384611725, "net_dimension": 512, "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 316}, "task": "trading", "freq": "daily", "dataset": "volatile"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2025-09-10T07:57:04</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_trading_daily_volatile_runs_batch</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>trial_005</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>0.1991</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1.6587</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.2018</v>
+      </c>
+      <c r="H43" t="n">
+        <v>-0.052</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.1148</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.1233</v>
+      </c>
+      <c r="K43" t="n">
+        <v>-0.1068</v>
+      </c>
+      <c r="L43" t="n">
+        <v>-0.0897</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 3.950916564838231e-05, "batch_size": 1024, "gamma": 0.9646752384611725, "net_dimension": 512, "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 317}, "task": "trading", "freq": "daily", "dataset": "volatile"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2025-09-10T08:01:23</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_trading_daily_volatile_runs_batch</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>trial_006</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>0.2209</v>
+      </c>
+      <c r="F44" t="n">
+        <v>1.6109</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.2239</v>
+      </c>
+      <c r="H44" t="n">
+        <v>-0.0348</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.1307</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.1233</v>
+      </c>
+      <c r="K44" t="n">
+        <v>-0.0796</v>
+      </c>
+      <c r="L44" t="n">
+        <v>-0.0897</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 3.950916564838231e-05, "batch_size": 1024, "gamma": 0.9646752384611725, "net_dimension": 512, "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 318}, "task": "trading", "freq": "daily", "dataset": "volatile"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2025-09-10T08:08:17</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_trading_daily_volatile_runs_batch</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>trial_000</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>0.1269</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.8951</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.1285</v>
+      </c>
+      <c r="H45" t="n">
+        <v>-0.1091</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.1471</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0.1233</v>
+      </c>
+      <c r="K45" t="n">
+        <v>-0.1428</v>
+      </c>
+      <c r="L45" t="n">
+        <v>-0.0897</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 312}, "task": "trading", "freq": "daily", "dataset": "volatile"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2025-09-10T08:12:45</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_trading_daily_volatile_runs_batch</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>trial_001</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>0.3582</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1.726</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.3632</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.0738</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0.1233</v>
+      </c>
+      <c r="K46" t="n">
+        <v>-0.1441</v>
+      </c>
+      <c r="L46" t="n">
+        <v>-0.0897</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 313}, "task": "trading", "freq": "daily", "dataset": "volatile"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2025-09-10T08:17:15</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_trading_daily_volatile_runs_batch</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>trial_002</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>0.2673</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1.7599</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.2709</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.0019</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0.1233</v>
+      </c>
+      <c r="K47" t="n">
+        <v>-0.129</v>
+      </c>
+      <c r="L47" t="n">
+        <v>-0.0897</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 314}, "task": "trading", "freq": "daily", "dataset": "volatile"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2025-09-10T08:21:44</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_trading_daily_volatile_runs_batch</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>trial_003</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>0.2649</v>
+      </c>
+      <c r="F48" t="n">
+        <v>1.7399</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.2685</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.1426</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.1233</v>
+      </c>
+      <c r="K48" t="n">
+        <v>-0.1154</v>
+      </c>
+      <c r="L48" t="n">
+        <v>-0.0897</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 315}, "task": "trading", "freq": "daily", "dataset": "volatile"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2025-09-10T08:26:07</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_trading_daily_volatile_runs_batch</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>trial_004</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>0.1721</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1.1038</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.1743</v>
+      </c>
+      <c r="H49" t="n">
+        <v>-0.07340000000000001</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.1567</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0.1233</v>
+      </c>
+      <c r="K49" t="n">
+        <v>-0.1646</v>
+      </c>
+      <c r="L49" t="n">
+        <v>-0.0897</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 316}, "task": "trading", "freq": "daily", "dataset": "volatile"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2025-09-10T08:30:29</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_trading_daily_volatile_runs_batch</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>trial_005</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>0.1291</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.9779</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.1307</v>
+      </c>
+      <c r="H50" t="n">
+        <v>-0.1074</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.1349</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0.1233</v>
+      </c>
+      <c r="K50" t="n">
+        <v>-0.076</v>
+      </c>
+      <c r="L50" t="n">
+        <v>-0.0897</v>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 317}, "task": "trading", "freq": "daily", "dataset": "volatile"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2025-09-10T08:34:59</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_trading_daily_volatile_runs_batch</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>trial_006</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>0.1397</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.9167999999999999</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.1414</v>
+      </c>
+      <c r="H51" t="n">
+        <v>-0.099</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.1579</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0.1233</v>
+      </c>
+      <c r="K51" t="n">
+        <v>-0.1402</v>
+      </c>
+      <c r="L51" t="n">
+        <v>-0.0897</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 318}, "task": "trading", "freq": "daily", "dataset": "volatile"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2025-09-10T08:39:31</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_trading_daily_volatile_runs_batch</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>trial_007</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>0.1491</v>
+      </c>
+      <c r="F52" t="n">
+        <v>1.0066</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0.151</v>
+      </c>
+      <c r="H52" t="n">
+        <v>-0.0916</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.151</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0.1233</v>
+      </c>
+      <c r="K52" t="n">
+        <v>-0.1316</v>
+      </c>
+      <c r="L52" t="n">
+        <v>-0.0897</v>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 319}, "task": "trading", "freq": "daily", "dataset": "volatile"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2025-09-10T17:37:09</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_trading_daily_volatile_runs_batch</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>trial_000</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>0.1888</v>
+      </c>
+      <c r="F53" t="n">
+        <v>1.3956</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.1913</v>
+      </c>
+      <c r="H53" t="n">
+        <v>-0.0601</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.1317</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0.1233</v>
+      </c>
+      <c r="K53" t="n">
+        <v>-0.0994</v>
+      </c>
+      <c r="L53" t="n">
+        <v>-0.0897</v>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 312}, "task": "trading", "freq": "daily", "dataset": "volatile"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2025-09-10T17:41:36</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_trading_daily_volatile_runs_batch</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>trial_001</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>0.1873</v>
+      </c>
+      <c r="F54" t="n">
+        <v>1.3225</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.1897</v>
+      </c>
+      <c r="H54" t="n">
+        <v>-0.0614</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.1386</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0.1233</v>
+      </c>
+      <c r="K54" t="n">
+        <v>-0.1358</v>
+      </c>
+      <c r="L54" t="n">
+        <v>-0.0897</v>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 313}, "task": "trading", "freq": "daily", "dataset": "volatile"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2025-09-10T17:46:03</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_trading_daily_volatile_runs_batch</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>trial_002</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>0.2716</v>
+      </c>
+      <c r="F55" t="n">
+        <v>1.622</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.2753</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.0053</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.1576</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0.1233</v>
+      </c>
+      <c r="K55" t="n">
+        <v>-0.1127</v>
+      </c>
+      <c r="L55" t="n">
+        <v>-0.0897</v>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 314}, "task": "trading", "freq": "daily", "dataset": "volatile"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2025-09-10T17:50:27</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_trading_daily_volatile_runs_batch</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>trial_003</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>0.1528</v>
+      </c>
+      <c r="F56" t="n">
+        <v>1.1112</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.1548</v>
+      </c>
+      <c r="H56" t="n">
+        <v>-0.0886</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.1381</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0.1233</v>
+      </c>
+      <c r="K56" t="n">
+        <v>-0.1012</v>
+      </c>
+      <c r="L56" t="n">
+        <v>-0.0897</v>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 315}, "task": "trading", "freq": "daily", "dataset": "volatile"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2025-09-10T17:54:54</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_trading_daily_volatile_runs_batch</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>trial_004</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>0.09569999999999999</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.7289</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0.0969</v>
+      </c>
+      <c r="H57" t="n">
+        <v>-0.1338</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.1404</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0.1233</v>
+      </c>
+      <c r="K57" t="n">
+        <v>-0.1285</v>
+      </c>
+      <c r="L57" t="n">
+        <v>-0.0897</v>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 316}, "task": "trading", "freq": "daily", "dataset": "volatile"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2025-09-10T17:59:14</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_trading_daily_volatile_runs_batch</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>trial_005</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>0.1456</v>
+      </c>
+      <c r="F58" t="n">
+        <v>1.1944</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.1475</v>
+      </c>
+      <c r="H58" t="n">
+        <v>-0.09429999999999999</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.1213</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0.1233</v>
+      </c>
+      <c r="K58" t="n">
+        <v>-0.09379999999999999</v>
+      </c>
+      <c r="L58" t="n">
+        <v>-0.0897</v>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 317}, "task": "trading", "freq": "daily", "dataset": "volatile"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2025-09-10T18:03:36</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_trading_daily_volatile_runs_batch</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>trial_006</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>0.2681</v>
+      </c>
+      <c r="F59" t="n">
+        <v>1.8178</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.2717</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.1375</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0.1233</v>
+      </c>
+      <c r="K59" t="n">
+        <v>-0.1621</v>
+      </c>
+      <c r="L59" t="n">
+        <v>-0.0897</v>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 318}, "task": "trading", "freq": "daily", "dataset": "volatile"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2025-09-10T18:07:57</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_trading_daily_volatile_runs_batch</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>trial_007</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>0.1535</v>
+      </c>
+      <c r="F60" t="n">
+        <v>1.298</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0.1555</v>
+      </c>
+      <c r="H60" t="n">
+        <v>-0.0881</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.1166</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0.1233</v>
+      </c>
+      <c r="K60" t="n">
+        <v>-0.09030000000000001</v>
+      </c>
+      <c r="L60" t="n">
+        <v>-0.0897</v>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 319}, "task": "trading", "freq": "daily", "dataset": "volatile"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2025-09-10T18:12:19</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_trading_daily_volatile_runs_batch</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>trial_008</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>0.2079</v>
+      </c>
+      <c r="F61" t="n">
+        <v>1.3965</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0.2107</v>
+      </c>
+      <c r="H61" t="n">
+        <v>-0.045</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.1444</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0.1233</v>
+      </c>
+      <c r="K61" t="n">
+        <v>-0.1278</v>
+      </c>
+      <c r="L61" t="n">
+        <v>-0.0897</v>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 320}, "task": "trading", "freq": "daily", "dataset": "volatile"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2025-09-10T18:16:39</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_trading_daily_volatile_runs_batch</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>trial_009</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>0.2236</v>
+      </c>
+      <c r="F62" t="n">
+        <v>1.6504</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0.2265</v>
+      </c>
+      <c r="H62" t="n">
+        <v>-0.0327</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.1288</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0.1233</v>
+      </c>
+      <c r="K62" t="n">
+        <v>-0.1224</v>
+      </c>
+      <c r="L62" t="n">
+        <v>-0.0897</v>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 321}, "task": "trading", "freq": "daily", "dataset": "volatile"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2025-09-10T18:20:59</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_trading_daily_volatile_runs_batch</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>trial_010</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>0.2261</v>
+      </c>
+      <c r="F63" t="n">
+        <v>1.5707</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0.2291</v>
+      </c>
+      <c r="H63" t="n">
+        <v>-0.0306</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.1374</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0.1233</v>
+      </c>
+      <c r="K63" t="n">
+        <v>-0.1277</v>
+      </c>
+      <c r="L63" t="n">
+        <v>-0.0897</v>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 322}, "task": "trading", "freq": "daily", "dataset": "volatile"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2025-09-10T18:25:19</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_trading_daily_volatile_runs_batch</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>trial_011</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>0.1532</v>
+      </c>
+      <c r="F64" t="n">
+        <v>1.1516</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0.1552</v>
+      </c>
+      <c r="H64" t="n">
+        <v>-0.0883</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0.1329</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0.1233</v>
+      </c>
+      <c r="K64" t="n">
+        <v>-0.0892</v>
+      </c>
+      <c r="L64" t="n">
+        <v>-0.0897</v>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 323}, "task": "trading", "freq": "daily", "dataset": "volatile"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2025-09-10T18:29:40</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_trading_daily_volatile_runs_batch</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>trial_012</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>0.2267</v>
+      </c>
+      <c r="F65" t="n">
+        <v>1.4136</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0.2298</v>
+      </c>
+      <c r="H65" t="n">
+        <v>-0.0301</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0.1548</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0.1233</v>
+      </c>
+      <c r="K65" t="n">
+        <v>-0.1341</v>
+      </c>
+      <c r="L65" t="n">
+        <v>-0.0897</v>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 324}, "task": "trading", "freq": "daily", "dataset": "volatile"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2025-09-10T18:34:00</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_trading_daily_volatile_runs_batch</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>trial_013</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>0.0721</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0.5447</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="H66" t="n">
+        <v>-0.1524</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0.1233</v>
+      </c>
+      <c r="K66" t="n">
+        <v>-0.1491</v>
+      </c>
+      <c r="L66" t="n">
+        <v>-0.0897</v>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 325}, "task": "trading", "freq": "daily", "dataset": "volatile"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2025-09-10T18:38:21</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_trading_daily_volatile_runs_batch</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>trial_014</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>0.1659</v>
+      </c>
+      <c r="F67" t="n">
+        <v>1.4619</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="H67" t="n">
+        <v>-0.07829999999999999</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0.1104</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0.1233</v>
+      </c>
+      <c r="K67" t="n">
+        <v>-0.07240000000000001</v>
+      </c>
+      <c r="L67" t="n">
+        <v>-0.0897</v>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 326}, "task": "trading", "freq": "daily", "dataset": "volatile"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2025-09-10T19:15:14</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>FIXED_sac_trading_daily_volatile_runs_batch</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>trial_000</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>sac</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>0.1304</v>
+      </c>
+      <c r="F68" t="n">
+        <v>1.0039</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0.1321</v>
+      </c>
+      <c r="H68" t="n">
+        <v>-0.1063</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0.1323</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0.1233</v>
+      </c>
+      <c r="K68" t="n">
+        <v>-0.1133</v>
+      </c>
+      <c r="L68" t="n">
+        <v>-0.0897</v>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 0.00038142226937329664, "batch_size": 512, "gamma": 0.9943398593021988, "net_dimension": 512, "net_dims": [512, 512], "target_step": 8192, "horizon_len": 2048, "repeat_times": 4.0, "buffer_size": 1000000, "buffer_init_size": 1024, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 312}, "task": "trading", "freq": "daily", "dataset": "volatile"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2025-09-10T19:21:23</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>FIXED_sac_trading_daily_volatile_runs_batch</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>trial_001</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>sac</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>0.1012</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0.7987</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0.1025</v>
+      </c>
+      <c r="H69" t="n">
+        <v>-0.1294</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0.1333</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0.1233</v>
+      </c>
+      <c r="K69" t="n">
+        <v>-0.0897</v>
+      </c>
+      <c r="L69" t="n">
+        <v>-0.0897</v>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 0.00038142226937329664, "batch_size": 512, "gamma": 0.9943398593021988, "net_dimension": 512, "net_dims": [512, 512], "target_step": 8192, "horizon_len": 2048, "repeat_times": 4.0, "buffer_size": 1000000, "buffer_init_size": 1024, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 313}, "task": "trading", "freq": "daily", "dataset": "volatile"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2025-09-10T19:27:35</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>FIXED_sac_trading_daily_volatile_runs_batch</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>trial_002</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>sac</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>0.1449</v>
+      </c>
+      <c r="F70" t="n">
+        <v>1.0852</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0.1467</v>
+      </c>
+      <c r="H70" t="n">
+        <v>-0.0949</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0.1345</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0.1233</v>
+      </c>
+      <c r="K70" t="n">
+        <v>-0.0977</v>
+      </c>
+      <c r="L70" t="n">
+        <v>-0.0897</v>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 0.00038142226937329664, "batch_size": 512, "gamma": 0.9943398593021988, "net_dimension": 512, "net_dims": [512, 512], "target_step": 8192, "horizon_len": 2048, "repeat_times": 4.0, "buffer_size": 1000000, "buffer_init_size": 1024, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 314}, "task": "trading", "freq": "daily", "dataset": "volatile"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2025-09-10T19:33:45</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>FIXED_sac_trading_daily_volatile_runs_batch</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>trial_003</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>sac</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>0.0925</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0.7207</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0.0936</v>
+      </c>
+      <c r="H71" t="n">
+        <v>-0.1363</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0.1372</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0.1233</v>
+      </c>
+      <c r="K71" t="n">
+        <v>-0.1062</v>
+      </c>
+      <c r="L71" t="n">
+        <v>-0.0897</v>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 0.00038142226937329664, "batch_size": 512, "gamma": 0.9943398593021988, "net_dimension": 512, "net_dims": [512, 512], "target_step": 8192, "horizon_len": 2048, "repeat_times": 4.0, "buffer_size": 1000000, "buffer_init_size": 1024, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 315}, "task": "trading", "freq": "daily", "dataset": "volatile"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2025-09-10T19:39:58</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>FIXED_sac_trading_daily_volatile_runs_batch</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>trial_004</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>sac</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="F72" t="n">
+        <v>1.466</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0.1874</v>
+      </c>
+      <c r="H72" t="n">
+        <v>-0.06320000000000001</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.1223</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0.1233</v>
+      </c>
+      <c r="K72" t="n">
+        <v>-0.07140000000000001</v>
+      </c>
+      <c r="L72" t="n">
+        <v>-0.0897</v>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 0.00038142226937329664, "batch_size": 512, "gamma": 0.9943398593021988, "net_dimension": 512, "net_dims": [512, 512], "target_step": 8192, "horizon_len": 2048, "repeat_times": 4.0, "buffer_size": 1000000, "buffer_init_size": 1024, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 316}, "task": "trading", "freq": "daily", "dataset": "volatile"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2025-09-10T19:46:10</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>FIXED_sac_trading_daily_volatile_runs_batch</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>trial_005</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>sac</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>0.07729999999999999</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0.659</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0.07829999999999999</v>
+      </c>
+      <c r="H73" t="n">
+        <v>-0.1483</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.1265</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0.1233</v>
+      </c>
+      <c r="K73" t="n">
+        <v>-0.0769</v>
+      </c>
+      <c r="L73" t="n">
+        <v>-0.0897</v>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 0.00038142226937329664, "batch_size": 512, "gamma": 0.9943398593021988, "net_dimension": 512, "net_dims": [512, 512], "target_step": 8192, "horizon_len": 2048, "repeat_times": 4.0, "buffer_size": 1000000, "buffer_init_size": 1024, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 317}, "task": "trading", "freq": "daily", "dataset": "volatile"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2025-09-10T19:52:18</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>FIXED_sac_trading_daily_volatile_runs_batch</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>trial_006</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>sac</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>0.2595</v>
+      </c>
+      <c r="F74" t="n">
+        <v>1.7436</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0.263</v>
+      </c>
+      <c r="H74" t="n">
+        <v>-0.0043</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0.1395</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0.1233</v>
+      </c>
+      <c r="K74" t="n">
+        <v>-0.0766</v>
+      </c>
+      <c r="L74" t="n">
+        <v>-0.0897</v>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 0.00038142226937329664, "batch_size": 512, "gamma": 0.9943398593021988, "net_dimension": 512, "net_dims": [512, 512], "target_step": 8192, "horizon_len": 2048, "repeat_times": 4.0, "buffer_size": 1000000, "buffer_init_size": 1024, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 318}, "task": "trading", "freq": "daily", "dataset": "volatile"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2025-09-10T19:58:24</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>FIXED_sac_trading_daily_volatile_runs_batch</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>trial_007</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>sac</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>0.08939999999999999</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0.8218</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0.0905</v>
+      </c>
+      <c r="H75" t="n">
+        <v>-0.1387</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0.1132</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0.1233</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-0.0684</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.0897</v>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 0.00038142226937329664, "batch_size": 512, "gamma": 0.9943398593021988, "net_dimension": 512, "net_dims": [512, 512], "target_step": 8192, "horizon_len": 2048, "repeat_times": 4.0, "buffer_size": 1000000, "buffer_init_size": 1024, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 319}, "task": "trading", "freq": "daily", "dataset": "volatile"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2025-09-10T20:04:35</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>FIXED_sac_trading_daily_volatile_runs_batch</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>trial_008</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>sac</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>0.1525</v>
+      </c>
+      <c r="F76" t="n">
+        <v>1.0681</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0.1545</v>
+      </c>
+      <c r="H76" t="n">
+        <v>-0.0888</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0.1442</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0.1233</v>
+      </c>
+      <c r="K76" t="n">
+        <v>-0.1303</v>
+      </c>
+      <c r="L76" t="n">
+        <v>-0.0897</v>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 0.00038142226937329664, "batch_size": 512, "gamma": 0.9943398593021988, "net_dimension": 512, "net_dims": [512, 512], "target_step": 8192, "horizon_len": 2048, "repeat_times": 4.0, "buffer_size": 1000000, "buffer_init_size": 1024, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 320}, "task": "trading", "freq": "daily", "dataset": "volatile"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2025-09-10T20:10:44</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>FIXED_sac_trading_daily_volatile_runs_batch</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>trial_009</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>sac</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>0.2058</v>
+      </c>
+      <c r="F77" t="n">
+        <v>1.5322</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0.2085</v>
+      </c>
+      <c r="H77" t="n">
+        <v>-0.0467</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0.1233</v>
+      </c>
+      <c r="K77" t="n">
+        <v>-0.0789</v>
+      </c>
+      <c r="L77" t="n">
+        <v>-0.0897</v>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 0.00038142226937329664, "batch_size": 512, "gamma": 0.9943398593021988, "net_dimension": 512, "net_dims": [512, 512], "target_step": 8192, "horizon_len": 2048, "repeat_times": 4.0, "buffer_size": 1000000, "buffer_init_size": 1024, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 321}, "task": "trading", "freq": "daily", "dataset": "volatile"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2025-09-10T20:16:55</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>FIXED_sac_trading_daily_volatile_runs_batch</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>trial_010</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>sac</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>0.1518</v>
+      </c>
+      <c r="F78" t="n">
+        <v>1.2613</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0.1537</v>
+      </c>
+      <c r="H78" t="n">
+        <v>-0.08939999999999999</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0.1233</v>
+      </c>
+      <c r="K78" t="n">
+        <v>-0.1031</v>
+      </c>
+      <c r="L78" t="n">
+        <v>-0.0897</v>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 0.00038142226937329664, "batch_size": 512, "gamma": 0.9943398593021988, "net_dimension": 512, "net_dims": [512, 512], "target_step": 8192, "horizon_len": 2048, "repeat_times": 4.0, "buffer_size": 1000000, "buffer_init_size": 1024, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 322}, "task": "trading", "freq": "daily", "dataset": "volatile"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2025-09-10T20:23:01</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>FIXED_sac_trading_daily_volatile_runs_batch</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>trial_011</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>sac</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>0.1645</v>
+      </c>
+      <c r="F79" t="n">
+        <v>1.1567</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0.1666</v>
+      </c>
+      <c r="H79" t="n">
+        <v>-0.0794</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0.1233</v>
+      </c>
+      <c r="K79" t="n">
+        <v>-0.1017</v>
+      </c>
+      <c r="L79" t="n">
+        <v>-0.0897</v>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 0.00038142226937329664, "batch_size": 512, "gamma": 0.9943398593021988, "net_dimension": 512, "net_dims": [512, 512], "target_step": 8192, "horizon_len": 2048, "repeat_times": 4.0, "buffer_size": 1000000, "buffer_init_size": 1024, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 323}, "task": "trading", "freq": "daily", "dataset": "volatile"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2025-09-10T20:29:07</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>FIXED_sac_trading_daily_volatile_runs_batch</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>trial_012</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>sac</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>0.2261</v>
+      </c>
+      <c r="F80" t="n">
+        <v>1.4947</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0.2291</v>
+      </c>
+      <c r="H80" t="n">
+        <v>-0.0307</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0.1451</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0.1233</v>
+      </c>
+      <c r="K80" t="n">
+        <v>-0.1073</v>
+      </c>
+      <c r="L80" t="n">
+        <v>-0.0897</v>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 0.00038142226937329664, "batch_size": 512, "gamma": 0.9943398593021988, "net_dimension": 512, "net_dims": [512, 512], "target_step": 8192, "horizon_len": 2048, "repeat_times": 4.0, "buffer_size": 1000000, "buffer_init_size": 1024, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 324}, "task": "trading", "freq": "daily", "dataset": "volatile"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2025-09-10T20:35:17</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>FIXED_sac_trading_daily_volatile_runs_batch</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>trial_013</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>sac</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>0.1344</v>
+      </c>
+      <c r="F81" t="n">
+        <v>1.0791</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0.1362</v>
+      </c>
+      <c r="H81" t="n">
+        <v>-0.1031</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0.1256</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0.1233</v>
+      </c>
+      <c r="K81" t="n">
+        <v>-0.0815</v>
+      </c>
+      <c r="L81" t="n">
+        <v>-0.0897</v>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 0.00038142226937329664, "batch_size": 512, "gamma": 0.9943398593021988, "net_dimension": 512, "net_dims": [512, 512], "target_step": 8192, "horizon_len": 2048, "repeat_times": 4.0, "buffer_size": 1000000, "buffer_init_size": 1024, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 325}, "task": "trading", "freq": "daily", "dataset": "volatile"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2025-09-10T20:41:23</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>FIXED_sac_trading_daily_volatile_runs_batch</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>trial_014</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>sac</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>0.1579</v>
+      </c>
+      <c r="F82" t="n">
+        <v>1.0676</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0.1599</v>
+      </c>
+      <c r="H82" t="n">
+        <v>-0.08459999999999999</v>
+      </c>
+      <c r="I82" t="n">
+        <v>0.1494</v>
+      </c>
+      <c r="J82" t="n">
+        <v>0.1233</v>
+      </c>
+      <c r="K82" t="n">
+        <v>-0.1256</v>
+      </c>
+      <c r="L82" t="n">
+        <v>-0.0897</v>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 0.00038142226937329664, "batch_size": 512, "gamma": 0.9943398593021988, "net_dimension": 512, "net_dims": [512, 512], "target_step": 8192, "horizon_len": 2048, "repeat_times": 4.0, "buffer_size": 1000000, "buffer_init_size": 1024, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 326}, "task": "trading", "freq": "daily", "dataset": "volatile"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2025-09-10T20:47:27</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>FIXED_sac_trading_daily_volatile_runs_batch</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>trial_015</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>sac</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>0.1741</v>
+      </c>
+      <c r="F83" t="n">
+        <v>1.3558</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0.1764</v>
+      </c>
+      <c r="H83" t="n">
+        <v>-0.0718</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0.1256</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0.1233</v>
+      </c>
+      <c r="K83" t="n">
+        <v>-0.0741</v>
+      </c>
+      <c r="L83" t="n">
+        <v>-0.0897</v>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 0.00038142226937329664, "batch_size": 512, "gamma": 0.9943398593021988, "net_dimension": 512, "net_dims": [512, 512], "target_step": 8192, "horizon_len": 2048, "repeat_times": 4.0, "buffer_size": 1000000, "buffer_init_size": 1024, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 327}, "task": "trading", "freq": "daily", "dataset": "volatile"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2025-09-10T20:53:35</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>FIXED_sac_trading_daily_volatile_runs_batch</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>trial_016</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>sac</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>0.07870000000000001</v>
+      </c>
+      <c r="F84" t="n">
+        <v>0.6913</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0.07969999999999999</v>
+      </c>
+      <c r="H84" t="n">
+        <v>-0.1472</v>
+      </c>
+      <c r="I84" t="n">
+        <v>0.1217</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0.1233</v>
+      </c>
+      <c r="K84" t="n">
+        <v>-0.08409999999999999</v>
+      </c>
+      <c r="L84" t="n">
+        <v>-0.0897</v>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 0.00038142226937329664, "batch_size": 512, "gamma": 0.9943398593021988, "net_dimension": 512, "net_dims": [512, 512], "target_step": 8192, "horizon_len": 2048, "repeat_times": 4.0, "buffer_size": 1000000, "buffer_init_size": 1024, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 328}, "task": "trading", "freq": "daily", "dataset": "volatile"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2025-09-10T20:59:47</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>FIXED_sac_trading_daily_volatile_runs_batch</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>trial_017</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>sac</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>0.0046</v>
+      </c>
+      <c r="F85" t="n">
+        <v>0.1018</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="H85" t="n">
+        <v>-0.2058</v>
+      </c>
+      <c r="I85" t="n">
+        <v>0.1348</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0.1233</v>
+      </c>
+      <c r="K85" t="n">
+        <v>-0.0968</v>
+      </c>
+      <c r="L85" t="n">
+        <v>-0.0897</v>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 0.00038142226937329664, "batch_size": 512, "gamma": 0.9943398593021988, "net_dimension": 512, "net_dims": [512, 512], "target_step": 8192, "horizon_len": 2048, "repeat_times": 4.0, "buffer_size": 1000000, "buffer_init_size": 1024, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 329}, "task": "trading", "freq": "daily", "dataset": "volatile"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2025-09-10T21:05:55</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>FIXED_sac_trading_daily_volatile_runs_batch</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>trial_018</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>sac</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>0.1849</v>
+      </c>
+      <c r="F86" t="n">
+        <v>1.4261</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0.1873</v>
+      </c>
+      <c r="H86" t="n">
+        <v>-0.06320000000000001</v>
+      </c>
+      <c r="I86" t="n">
+        <v>0.126</v>
+      </c>
+      <c r="J86" t="n">
+        <v>0.1233</v>
+      </c>
+      <c r="K86" t="n">
+        <v>-0.0823</v>
+      </c>
+      <c r="L86" t="n">
+        <v>-0.0897</v>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 0.00038142226937329664, "batch_size": 512, "gamma": 0.9943398593021988, "net_dimension": 512, "net_dims": [512, 512], "target_step": 8192, "horizon_len": 2048, "repeat_times": 4.0, "buffer_size": 1000000, "buffer_init_size": 1024, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 330}, "task": "trading", "freq": "daily", "dataset": "volatile"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2025-09-10T21:11:55</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>FIXED_sac_trading_daily_volatile_runs_batch</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>trial_019</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>sac</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>0.0926</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0.7135</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0.09379999999999999</v>
+      </c>
+      <c r="H87" t="n">
+        <v>-0.1362</v>
+      </c>
+      <c r="I87" t="n">
+        <v>0.1392</v>
+      </c>
+      <c r="J87" t="n">
+        <v>0.1233</v>
+      </c>
+      <c r="K87" t="n">
+        <v>-0.1097</v>
+      </c>
+      <c r="L87" t="n">
+        <v>-0.0897</v>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 0.00038142226937329664, "batch_size": 512, "gamma": 0.9943398593021988, "net_dimension": 512, "net_dims": [512, 512], "target_step": 8192, "horizon_len": 2048, "repeat_times": 4.0, "buffer_size": 1000000, "buffer_init_size": 1024, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 331}, "task": "trading", "freq": "daily", "dataset": "volatile"}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fixed_trading_daily_volatile.xlsx
+++ b/fixed_trading_daily_volatile.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M87"/>
+  <dimension ref="A1:M90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4881,6 +4881,159 @@
         </is>
       </c>
     </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2025-09-11T11:52:43</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>FIXED_ppo_trading_daily_volatile_runs_batch</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>trial_000</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>0.212</v>
+      </c>
+      <c r="F88" t="n">
+        <v>1.6012</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0.2148</v>
+      </c>
+      <c r="H88" t="n">
+        <v>-0.0418</v>
+      </c>
+      <c r="I88" t="n">
+        <v>0.1265</v>
+      </c>
+      <c r="J88" t="n">
+        <v>0.1233</v>
+      </c>
+      <c r="K88" t="n">
+        <v>-0.1215</v>
+      </c>
+      <c r="L88" t="n">
+        <v>-0.0897</v>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 312}, "task": "trading", "freq": "daily", "dataset": "volatile"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2025-09-11T11:56:44</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>FIXED_ppo_trading_daily_volatile_runs_batch</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>trial_001</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>0.1608</v>
+      </c>
+      <c r="F89" t="n">
+        <v>1.2382</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0.1629</v>
+      </c>
+      <c r="H89" t="n">
+        <v>-0.0823</v>
+      </c>
+      <c r="I89" t="n">
+        <v>0.1285</v>
+      </c>
+      <c r="J89" t="n">
+        <v>0.1233</v>
+      </c>
+      <c r="K89" t="n">
+        <v>-0.1234</v>
+      </c>
+      <c r="L89" t="n">
+        <v>-0.0897</v>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 313}, "task": "trading", "freq": "daily", "dataset": "volatile"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2025-09-11T12:00:55</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>FIXED_ppo_trading_daily_volatile_runs_batch</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>trial_002</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>0.0471</v>
+      </c>
+      <c r="F90" t="n">
+        <v>0.4708</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0.0477</v>
+      </c>
+      <c r="H90" t="n">
+        <v>-0.1722</v>
+      </c>
+      <c r="I90" t="n">
+        <v>0.1123</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0.1233</v>
+      </c>
+      <c r="K90" t="n">
+        <v>-0.08409999999999999</v>
+      </c>
+      <c r="L90" t="n">
+        <v>-0.0897</v>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 314}, "task": "trading", "freq": "daily", "dataset": "volatile"}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
